--- a/salidas/empresas/OXY.xlsx
+++ b/salidas/empresas/OXY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>27.36648941040039</v>
+        <v>27.36649322509766</v>
       </c>
       <c r="C2" t="n">
         <v>46.80609130859375</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>25.63840293884277</v>
+        <v>25.63838768005371</v>
       </c>
       <c r="C3" t="n">
         <v>43.85047149658203</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>26.05231857299805</v>
+        <v>26.05231094360352</v>
       </c>
       <c r="C4" t="n">
         <v>44.38219451904297</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>28.88952445983887</v>
+        <v>28.88951301574707</v>
       </c>
       <c r="C5" t="n">
         <v>49.21561431884766</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>27.86314964294434</v>
+        <v>27.86318588256836</v>
       </c>
       <c r="C6" t="n">
         <v>47.4671516418457</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>28.94225692749023</v>
+        <v>28.94225120544434</v>
       </c>
       <c r="C7" t="n">
         <v>49.12459945678711</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>30.40982818603516</v>
+        <v>30.40982437133789</v>
       </c>
       <c r="C8" t="n">
         <v>51.61555862426758</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>28.78138160705566</v>
+        <v>28.7813835144043</v>
       </c>
       <c r="C9" t="n">
         <v>48.8515510559082</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>27.27324867248535</v>
+        <v>27.27325057983398</v>
       </c>
       <c r="C10" t="n">
         <v>46.09233474731445</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>26.60998153686523</v>
+        <v>26.60999488830566</v>
       </c>
       <c r="C11" t="n">
         <v>44.97140121459961</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>28.53742218017578</v>
+        <v>28.53742027282715</v>
       </c>
       <c r="C12" t="n">
         <v>48.22881317138672</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>27.80233192443848</v>
+        <v>27.80233764648438</v>
       </c>
       <c r="C13" t="n">
         <v>46.78213882446289</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>26.3960018157959</v>
+        <v>26.39598846435547</v>
       </c>
       <c r="C14" t="n">
         <v>44.41572570800781</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>28.21111869812012</v>
+        <v>28.21111297607422</v>
       </c>
       <c r="C16" t="n">
         <v>47.24200820922852</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>29.0063648223877</v>
+        <v>29.0063591003418</v>
       </c>
       <c r="C17" t="n">
         <v>48.57371520996094</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>31.44930076599121</v>
+        <v>31.44930839538574</v>
       </c>
       <c r="C18" t="n">
         <v>52.66463470458984</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>33.23958587646484</v>
+        <v>33.23958206176758</v>
       </c>
       <c r="C19" t="n">
         <v>55.45259475708008</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.57341003417969</v>
+        <v>32.57339859008789</v>
       </c>
       <c r="C20" t="n">
         <v>54.34124374389648</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>32.55618667602539</v>
+        <v>32.55617141723633</v>
       </c>
       <c r="C21" t="n">
         <v>54.31250381469727</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>36.95842742919922</v>
+        <v>36.95844650268555</v>
       </c>
       <c r="C22" t="n">
         <v>61.39257431030273</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>39.82490158081055</v>
+        <v>39.82489395141602</v>
       </c>
       <c r="C23" t="n">
         <v>66.15414428710938</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>40.24015808105469</v>
+        <v>40.24017715454102</v>
       </c>
       <c r="C24" t="n">
         <v>66.84394836425781</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>44.56282043457031</v>
+        <v>44.56280136108398</v>
       </c>
       <c r="C25" t="n">
         <v>73.76114654541016</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>39.2435188293457</v>
+        <v>39.24351501464844</v>
       </c>
       <c r="C26" t="n">
         <v>64.95656585693359</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>44.78274917602539</v>
+        <v>44.78275299072266</v>
       </c>
       <c r="C27" t="n">
         <v>74.12521362304688</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>42.48711395263672</v>
+        <v>42.48712158203125</v>
       </c>
       <c r="C28" t="n">
         <v>70.10135650634766</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>48.31699371337891</v>
+        <v>48.31696319580078</v>
       </c>
       <c r="C29" t="n">
         <v>79.72029113769531</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>53.38034820556641</v>
+        <v>53.38035202026367</v>
       </c>
       <c r="C30" t="n">
         <v>88.0745849609375</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>52.36123275756836</v>
+        <v>52.36123657226562</v>
       </c>
       <c r="C31" t="n">
         <v>86.09140014648438</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>45.93407440185547</v>
+        <v>45.9340705871582</v>
       </c>
       <c r="C32" t="n">
         <v>75.52397918701172</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>46.24289321899414</v>
+        <v>46.2429084777832</v>
       </c>
       <c r="C33" t="n">
         <v>76.03175354003906</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>41.23114776611328</v>
+        <v>41.23114395141602</v>
       </c>
       <c r="C34" t="n">
         <v>67.49542999267578</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>32.5050163269043</v>
+        <v>32.50500106811523</v>
       </c>
       <c r="C35" t="n">
         <v>53.21073150634766</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>31.6856575012207</v>
+        <v>31.6856517791748</v>
       </c>
       <c r="C36" t="n">
         <v>51.86944580078125</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>35.35431671142578</v>
+        <v>35.35430908203125</v>
       </c>
       <c r="C37" t="n">
         <v>57.47410583496094</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>32.14831924438477</v>
+        <v>32.1483268737793</v>
       </c>
       <c r="C38" t="n">
         <v>52.26224899291992</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>30.56889915466309</v>
+        <v>30.56890106201172</v>
       </c>
       <c r="C39" t="n">
         <v>49.69464492797852</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>33.00767517089844</v>
+        <v>33.0076789855957</v>
       </c>
       <c r="C40" t="n">
         <v>53.31611633300781</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>33.38726806640625</v>
+        <v>33.38727569580078</v>
       </c>
       <c r="C41" t="n">
         <v>53.92927551269531</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>39.8049430847168</v>
+        <v>39.80493927001953</v>
       </c>
       <c r="C42" t="n">
         <v>64.29550170898438</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>39.22266387939453</v>
+        <v>39.22266006469727</v>
       </c>
       <c r="C43" t="n">
         <v>63.05002212524414</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>42.51852798461914</v>
+        <v>42.5185432434082</v>
       </c>
       <c r="C44" t="n">
         <v>68.34809875488281</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>43.56749725341797</v>
+        <v>43.56748199462891</v>
       </c>
       <c r="C45" t="n">
         <v>70.03428649902344</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>46.93927383422852</v>
+        <v>46.93926239013672</v>
       </c>
       <c r="C46" t="n">
         <v>75.11201477050781</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>45.43048858642578</v>
+        <v>45.43049621582031</v>
       </c>
       <c r="C47" t="n">
         <v>72.69770050048828</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>48.37017822265625</v>
+        <v>48.37018966674805</v>
       </c>
       <c r="C48" t="n">
         <v>77.40177917480469</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>48.91175842285156</v>
+        <v>48.91176986694336</v>
       </c>
       <c r="C49" t="n">
         <v>77.93829345703125</v>
@@ -1424,7 +1436,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>48.00989532470703</v>
+        <v>48.00990295410156</v>
       </c>
       <c r="C51" t="n">
         <v>76.50120544433594</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>51.03528213500977</v>
+        <v>51.03530120849609</v>
       </c>
       <c r="C52" t="n">
         <v>80.99451446533203</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>53.5224609375</v>
+        <v>53.52248382568359</v>
       </c>
       <c r="C53" t="n">
         <v>84.94172668457031</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>49.8098258972168</v>
+        <v>49.80982208251953</v>
       </c>
       <c r="C54" t="n">
         <v>79.04964447021484</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>46.79994964599609</v>
+        <v>46.79994201660156</v>
       </c>
       <c r="C55" t="n">
         <v>73.91443634033203</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>47.27309417724609</v>
+        <v>47.27310943603516</v>
       </c>
       <c r="C56" t="n">
         <v>74.66172790527344</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>44.3310432434082</v>
+        <v>44.33103179931641</v>
       </c>
       <c r="C57" t="n">
         <v>70.01512908935547</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>47.73482131958008</v>
+        <v>47.73481750488281</v>
       </c>
       <c r="C58" t="n">
         <v>75.01621246337891</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>47.93597793579102</v>
+        <v>47.93598556518555</v>
       </c>
       <c r="C59" t="n">
         <v>75.33236694335938</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>53.75197601318359</v>
+        <v>53.75197219848633</v>
       </c>
       <c r="C60" t="n">
         <v>84.47227478027344</v>
@@ -1699,7 +1711,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>59.18254470825195</v>
+        <v>59.18254089355469</v>
       </c>
       <c r="C62" t="n">
         <v>92.62538146972656</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>62.42080307006836</v>
+        <v>62.42082595825195</v>
       </c>
       <c r="C63" t="n">
         <v>97.69351959228516</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>64.2489013671875</v>
+        <v>64.24890899658203</v>
       </c>
       <c r="C64" t="n">
         <v>100.1078414916992</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>70.27471160888672</v>
+        <v>70.27474975585938</v>
       </c>
       <c r="C65" t="n">
         <v>109.4968414306641</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>66.31489562988281</v>
+        <v>66.31488800048828</v>
       </c>
       <c r="C66" t="n">
         <v>103.3269271850586</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>64.26356506347656</v>
+        <v>64.26357269287109</v>
       </c>
       <c r="C67" t="n">
         <v>99.67671203613281</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>60.64393615722656</v>
+        <v>60.64393997192383</v>
       </c>
       <c r="C68" t="n">
         <v>94.06246948242188</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>53.57766723632812</v>
+        <v>53.57768249511719</v>
       </c>
       <c r="C69" t="n">
         <v>83.10224914550781</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>44.41117095947266</v>
+        <v>44.41118240356445</v>
       </c>
       <c r="C70" t="n">
         <v>68.50138854980469</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>57.72832107543945</v>
+        <v>57.72830963134766</v>
       </c>
       <c r="C71" t="n">
         <v>89.04222869873047</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>61.43032073974609</v>
+        <v>61.43026733398438</v>
       </c>
       <c r="C72" t="n">
         <v>94.75227355957031</v>
@@ -2039,7 +2051,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>62.26546096801758</v>
+        <v>62.26546859741211</v>
       </c>
       <c r="C74" t="n">
         <v>95.58578491210938</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>65.13627624511719</v>
+        <v>65.13628387451172</v>
       </c>
       <c r="C75" t="n">
         <v>99.99286651611328</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>59.7514762878418</v>
+        <v>59.75148010253906</v>
       </c>
       <c r="C76" t="n">
         <v>91.23619079589844</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>57.23540878295898</v>
+        <v>57.23540115356445</v>
       </c>
       <c r="C77" t="n">
         <v>87.39436340332031</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>49.73745727539062</v>
+        <v>49.73746109008789</v>
       </c>
       <c r="C78" t="n">
         <v>75.94552612304688</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>54.17621994018555</v>
+        <v>54.17623519897461</v>
       </c>
       <c r="C79" t="n">
         <v>82.17292785644531</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>54.97209167480469</v>
+        <v>54.97208786010742</v>
       </c>
       <c r="C80" t="n">
         <v>83.38008880615234</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>53.69615173339844</v>
+        <v>53.69618988037109</v>
       </c>
       <c r="C81" t="n">
         <v>81.44480133056641</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>54.71690368652344</v>
+        <v>54.71688842773438</v>
       </c>
       <c r="C82" t="n">
         <v>82.45076751708984</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>50.20271301269531</v>
+        <v>50.20272827148438</v>
       </c>
       <c r="C83" t="n">
         <v>75.64852905273438</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>47.81846618652344</v>
+        <v>47.8184700012207</v>
       </c>
       <c r="C84" t="n">
         <v>72.05580139160156</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>49.06427383422852</v>
+        <v>49.06428146362305</v>
       </c>
       <c r="C85" t="n">
         <v>73.39708709716797</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>56.53182601928711</v>
+        <v>56.53183364868164</v>
       </c>
       <c r="C86" t="n">
         <v>84.56808471679688</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>52.72758865356445</v>
+        <v>52.72760391235352</v>
       </c>
       <c r="C87" t="n">
         <v>78.877197265625</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>50.58409118652344</v>
+        <v>50.58408355712891</v>
       </c>
       <c r="C88" t="n">
         <v>75.08327484130859</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>57.61308288574219</v>
+        <v>57.61308670043945</v>
       </c>
       <c r="C89" t="n">
         <v>85.51656341552734</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>59.42679595947266</v>
+        <v>59.42680740356445</v>
       </c>
       <c r="C90" t="n">
         <v>88.20871734619141</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>57.99118423461914</v>
+        <v>57.99115371704102</v>
       </c>
       <c r="C91" t="n">
         <v>85.48782348632812</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>57.87417221069336</v>
+        <v>57.87418746948242</v>
       </c>
       <c r="C92" t="n">
         <v>85.31536865234375</v>
@@ -2619,7 +2631,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>61.22894668579102</v>
+        <v>61.22893142700195</v>
       </c>
       <c r="C94" t="n">
         <v>89.6170654296875</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>62.89154815673828</v>
+        <v>62.89152908325195</v>
       </c>
       <c r="C95" t="n">
         <v>92.05054473876953</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>62.15840530395508</v>
+        <v>62.15841674804688</v>
       </c>
       <c r="C96" t="n">
         <v>90.97750854492188</v>
@@ -2735,7 +2747,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>63.61533737182617</v>
+        <v>63.6153564453125</v>
       </c>
       <c r="C99" t="n">
         <v>92.47209167480469</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>63.27505493164062</v>
+        <v>63.27504348754883</v>
       </c>
       <c r="C100" t="n">
         <v>91.29367065429688</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>63.58052062988281</v>
+        <v>63.58050155639648</v>
       </c>
       <c r="C101" t="n">
         <v>91.73438262939453</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>66.19676971435547</v>
+        <v>66.19676208496094</v>
       </c>
       <c r="C102" t="n">
         <v>95.50914001464844</v>
@@ -2909,7 +2921,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>65.34830474853516</v>
+        <v>65.34832763671875</v>
       </c>
       <c r="C104" t="n">
         <v>93.6121826171875</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>69.37446594238281</v>
+        <v>69.37445068359375</v>
       </c>
       <c r="C105" t="n">
         <v>99.37970733642578</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>64.76526641845703</v>
+        <v>64.76528167724609</v>
       </c>
       <c r="C106" t="n">
         <v>92.11760711669922</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>59.9019660949707</v>
+        <v>59.90196990966797</v>
       </c>
       <c r="C107" t="n">
         <v>85.20040130615234</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>53.7319221496582</v>
+        <v>53.73193740844727</v>
       </c>
       <c r="C108" t="n">
         <v>76.424560546875</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>57.08264541625977</v>
+        <v>57.08262252807617</v>
       </c>
       <c r="C109" t="n">
         <v>80.47296142578125</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>56.65069961547852</v>
+        <v>56.65068817138672</v>
       </c>
       <c r="C110" t="n">
         <v>79.86399841308594</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>55.14943695068359</v>
+        <v>55.14944076538086</v>
       </c>
       <c r="C111" t="n">
         <v>77.74760437011719</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>52.17856979370117</v>
+        <v>52.17856597900391</v>
       </c>
       <c r="C112" t="n">
         <v>72.87590026855469</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>57.25347900390625</v>
+        <v>57.25347518920898</v>
       </c>
       <c r="C113" t="n">
         <v>79.96382904052734</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>55.88826751708984</v>
+        <v>55.88826370239258</v>
       </c>
       <c r="C114" t="n">
         <v>78.05707550048828</v>
@@ -3255,11 +3267,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>56.12023544311523</v>
+        <v>56.12020874023438</v>
       </c>
       <c r="C115" t="n">
         <v>77.63779449462891</v>
@@ -3282,11 +3294,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>50.65757751464844</v>
+        <v>50.6575927734375</v>
       </c>
       <c r="C116" t="n">
         <v>70.08065795898438</v>
@@ -3309,11 +3321,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>52.68534469604492</v>
+        <v>52.68532943725586</v>
       </c>
       <c r="C117" t="n">
         <v>72.88587951660156</v>
@@ -3336,11 +3348,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>48.25464248657227</v>
+        <v>48.25464630126953</v>
       </c>
       <c r="C118" t="n">
         <v>66.03754425048828</v>
@@ -3363,11 +3375,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>54.37493515014648</v>
+        <v>54.37493133544922</v>
       </c>
       <c r="C119" t="n">
         <v>74.41328430175781</v>
@@ -3390,11 +3402,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>55.14087295532227</v>
+        <v>55.140869140625</v>
       </c>
       <c r="C120" t="n">
         <v>75.46149444580078</v>
@@ -3417,11 +3429,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>49.8591194152832</v>
+        <v>49.85910797119141</v>
       </c>
       <c r="C121" t="n">
         <v>67.49506378173828</v>
@@ -3444,11 +3456,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>50.7588005065918</v>
+        <v>50.75880813598633</v>
       </c>
       <c r="C122" t="n">
         <v>68.71298980712891</v>
@@ -3471,11 +3483,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>50.83786392211914</v>
+        <v>50.83786773681641</v>
       </c>
       <c r="C123" t="n">
         <v>68.81999969482422</v>
@@ -3498,11 +3510,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>51.09449768066406</v>
+        <v>51.094482421875</v>
       </c>
       <c r="C124" t="n">
         <v>68.43000030517578</v>
@@ -3525,11 +3537,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>57.23208618164062</v>
+        <v>57.23208999633789</v>
       </c>
       <c r="C125" t="n">
         <v>76.65000152587891</v>
@@ -3552,11 +3564,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>56.32862854003906</v>
+        <v>56.3286247253418</v>
       </c>
       <c r="C126" t="n">
         <v>75.44000244140625</v>
@@ -3579,11 +3591,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>56.97410202026367</v>
+        <v>56.97411346435547</v>
       </c>
       <c r="C127" t="n">
         <v>75.55999755859375</v>
@@ -3606,11 +3618,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>56.34827041625977</v>
+        <v>56.34826278686523</v>
       </c>
       <c r="C128" t="n">
         <v>74.73000335693359</v>
@@ -3633,7 +3645,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3660,11 +3672,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>55.52448654174805</v>
+        <v>55.52447128295898</v>
       </c>
       <c r="C130" t="n">
         <v>72.91999816894531</v>
@@ -3687,11 +3699,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>55.51688003540039</v>
+        <v>55.51689147949219</v>
       </c>
       <c r="C131" t="n">
         <v>72.91000366210938</v>
@@ -3714,11 +3726,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>54.33663940429688</v>
+        <v>54.33662796020508</v>
       </c>
       <c r="C132" t="n">
         <v>71.36000061035156</v>
@@ -3741,11 +3753,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>54.8294563293457</v>
+        <v>54.82946395874023</v>
       </c>
       <c r="C133" t="n">
         <v>71.23000335693359</v>
@@ -3768,11 +3780,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>52.16614151000977</v>
+        <v>52.16611099243164</v>
       </c>
       <c r="C134" t="n">
         <v>67.76999664306641</v>
@@ -3795,11 +3807,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>50.457275390625</v>
+        <v>50.45727157592773</v>
       </c>
       <c r="C135" t="n">
         <v>65.55000305175781</v>
@@ -3822,11 +3834,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>49.35121917724609</v>
+        <v>49.35123443603516</v>
       </c>
       <c r="C136" t="n">
         <v>63.36000061035156</v>
@@ -3849,11 +3861,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>47.93361282348633</v>
+        <v>47.93362045288086</v>
       </c>
       <c r="C137" t="n">
         <v>61.54000091552734</v>
@@ -3876,11 +3888,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>45.90067672729492</v>
+        <v>45.90067291259766</v>
       </c>
       <c r="C138" t="n">
         <v>58.93000030517578</v>
@@ -3903,11 +3915,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>47.21490859985352</v>
+        <v>47.21490478515625</v>
       </c>
       <c r="C139" t="n">
         <v>59.86999893188477</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>48.83947372436523</v>
+        <v>48.83946228027344</v>
       </c>
       <c r="C140" t="n">
         <v>61.93000030517578</v>
@@ -3957,11 +3969,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>47.08084106445312</v>
+        <v>47.08082962036133</v>
       </c>
       <c r="C141" t="n">
         <v>59.70000076293945</v>
@@ -3986,11 +3998,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>51.27577972412109</v>
+        <v>51.27578735351562</v>
       </c>
       <c r="C142" t="n">
         <v>64.20999908447266</v>
@@ -4015,7 +4027,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4044,11 +4056,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>56.29876327514648</v>
+        <v>56.29875564575195</v>
       </c>
       <c r="C144" t="n">
         <v>70.5</v>
@@ -4073,11 +4085,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>59.48208618164062</v>
+        <v>59.4820671081543</v>
       </c>
       <c r="C145" t="n">
         <v>73.66000366210938</v>
@@ -4102,11 +4114,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>60.53993606567383</v>
+        <v>60.53995513916016</v>
       </c>
       <c r="C146" t="n">
         <v>74.97000122070312</v>
@@ -4131,11 +4143,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>52.97344970703125</v>
+        <v>52.97345352172852</v>
       </c>
       <c r="C147" t="n">
         <v>65.59999847412109</v>
@@ -4160,11 +4172,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>53.08364486694336</v>
+        <v>53.08364868164062</v>
       </c>
       <c r="C148" t="n">
         <v>64.95999908447266</v>
@@ -4189,11 +4201,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>63.13488006591797</v>
+        <v>63.13488388061523</v>
       </c>
       <c r="C149" t="n">
         <v>77.26000213623047</v>
@@ -4218,11 +4230,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>68.80605316162109</v>
+        <v>68.80606842041016</v>
       </c>
       <c r="C150" t="n">
         <v>84.19999694824219</v>
@@ -4247,11 +4259,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>68.99547576904297</v>
+        <v>68.99545288085938</v>
       </c>
       <c r="C151" t="n">
         <v>83.68000030517578</v>
@@ -4276,11 +4288,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>69.20159149169922</v>
+        <v>69.20160675048828</v>
       </c>
       <c r="C152" t="n">
         <v>83.93000030517578</v>
@@ -4305,11 +4317,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>65.85405731201172</v>
+        <v>65.85404968261719</v>
       </c>
       <c r="C153" t="n">
         <v>79.87000274658203</v>
@@ -4334,11 +4346,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>68.43862915039062</v>
+        <v>68.43862152099609</v>
       </c>
       <c r="C154" t="n">
         <v>82.16999816894531</v>
@@ -4363,11 +4375,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>55.86197280883789</v>
+        <v>55.86198425292969</v>
       </c>
       <c r="C155" t="n">
         <v>67.06999969482422</v>
@@ -4392,11 +4404,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>58.52721786499023</v>
+        <v>58.5272216796875</v>
       </c>
       <c r="C156" t="n">
         <v>70.26999664306641</v>
@@ -4421,11 +4433,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>51.72030639648438</v>
+        <v>51.72031402587891</v>
       </c>
       <c r="C157" t="n">
         <v>61.38000106811523</v>
@@ -4450,7 +4462,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4479,11 +4491,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>55.73963928222656</v>
+        <v>55.7396354675293</v>
       </c>
       <c r="C159" t="n">
         <v>66.15000152587891</v>
@@ -4508,11 +4520,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>56.45156478881836</v>
+        <v>56.45154190063477</v>
       </c>
       <c r="C160" t="n">
         <v>66.19999694824219</v>
@@ -4537,7 +4549,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4566,11 +4578,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>42.44099426269531</v>
+        <v>42.44100189208984</v>
       </c>
       <c r="C162" t="n">
         <v>49.77000045776367</v>
@@ -4595,11 +4607,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>43.56887054443359</v>
+        <v>43.56887817382812</v>
       </c>
       <c r="C163" t="n">
         <v>50.27999877929688</v>
@@ -4624,11 +4636,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>44.50474166870117</v>
+        <v>44.50471496582031</v>
       </c>
       <c r="C164" t="n">
         <v>51.36000061035156</v>
@@ -4653,11 +4665,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>37.676513671875</v>
+        <v>37.6765022277832</v>
       </c>
       <c r="C165" t="n">
         <v>43.47999954223633</v>
@@ -4682,11 +4694,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>39.21584320068359</v>
+        <v>39.21586608886719</v>
       </c>
       <c r="C166" t="n">
         <v>44.47000122070312</v>
@@ -4711,11 +4723,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>35.71491241455078</v>
+        <v>35.71490859985352</v>
       </c>
       <c r="C167" t="n">
         <v>40.5</v>
@@ -4740,11 +4752,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>34.012939453125</v>
+        <v>34.01293563842773</v>
       </c>
       <c r="C168" t="n">
         <v>38.56999969482422</v>
@@ -4769,11 +4781,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>37.09218978881836</v>
+        <v>37.09218597412109</v>
       </c>
       <c r="C169" t="n">
         <v>41.20999908447266</v>
@@ -4798,11 +4810,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>35.75106048583984</v>
+        <v>35.75107192993164</v>
       </c>
       <c r="C170" t="n">
         <v>39.72000122070312</v>
@@ -4827,11 +4839,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>29.46853256225586</v>
+        <v>29.46853446960449</v>
       </c>
       <c r="C171" t="n">
         <v>32.7400016784668</v>
@@ -4854,11 +4866,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>10.73874092102051</v>
+        <v>10.73873996734619</v>
       </c>
       <c r="C172" t="n">
         <v>11.57999992370605</v>
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>15.3940486907959</v>
+        <v>15.39404964447021</v>
       </c>
       <c r="C173" t="n">
         <v>16.60000038146973</v>
@@ -4908,11 +4920,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>12.00921154022217</v>
+        <v>12.00921440124512</v>
       </c>
       <c r="C174" t="n">
         <v>12.94999980926514</v>
@@ -4935,11 +4947,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>16.98029899597168</v>
+        <v>16.98030281066895</v>
       </c>
       <c r="C175" t="n">
         <v>18.29999923706055</v>
@@ -4962,11 +4974,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>14.6049165725708</v>
+        <v>14.60491466522217</v>
       </c>
       <c r="C176" t="n">
         <v>15.73999977111816</v>
@@ -4989,11 +5001,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>11.82125854492188</v>
+        <v>11.82125949859619</v>
       </c>
       <c r="C177" t="n">
         <v>12.73999977111816</v>
@@ -5016,7 +5028,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>8.479887962341309</v>
+        <v>8.479890823364258</v>
       </c>
       <c r="C179" t="n">
         <v>9.130000114440918</v>
@@ -5070,11 +5082,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>14.63779830932617</v>
+        <v>14.63779735565186</v>
       </c>
       <c r="C180" t="n">
         <v>15.76000022888184</v>
@@ -5097,11 +5109,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>16.08583450317383</v>
+        <v>16.08583068847656</v>
       </c>
       <c r="C181" t="n">
         <v>17.30999946594238</v>
@@ -5124,11 +5136,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>18.64135360717773</v>
+        <v>18.64135551452637</v>
       </c>
       <c r="C182" t="n">
         <v>20.05999946594238</v>
@@ -5151,11 +5163,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>24.72813987731934</v>
+        <v>24.72814178466797</v>
       </c>
       <c r="C183" t="n">
         <v>26.61000061035156</v>
@@ -5178,11 +5190,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>24.7457447052002</v>
+        <v>24.74574661254883</v>
       </c>
       <c r="C184" t="n">
         <v>26.6200008392334</v>
@@ -5205,11 +5217,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>23.57445907592773</v>
+        <v>23.57446098327637</v>
       </c>
       <c r="C185" t="n">
         <v>25.36000061035156</v>
@@ -5232,11 +5244,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>24.13221549987793</v>
+        <v>24.13221168518066</v>
       </c>
       <c r="C186" t="n">
         <v>25.95999908447266</v>
@@ -5259,11 +5271,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>29.07830429077148</v>
+        <v>29.07831382751465</v>
       </c>
       <c r="C187" t="n">
         <v>31.27000045776367</v>
@@ -5286,11 +5298,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>24.27067375183105</v>
+        <v>24.27066993713379</v>
       </c>
       <c r="C188" t="n">
         <v>26.10000038146973</v>
@@ -5313,11 +5325,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>23.88940620422363</v>
+        <v>23.88941192626953</v>
       </c>
       <c r="C189" t="n">
         <v>25.69000053405762</v>
@@ -5340,11 +5352,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>27.51780891418457</v>
+        <v>27.5178108215332</v>
       </c>
       <c r="C190" t="n">
         <v>29.57999992370605</v>
@@ -5367,11 +5379,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>31.19243049621582</v>
+        <v>31.19243621826172</v>
       </c>
       <c r="C191" t="n">
         <v>33.52999877929688</v>
@@ -5394,7 +5406,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5421,11 +5433,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>26.97770881652832</v>
+        <v>26.97770690917969</v>
       </c>
       <c r="C193" t="n">
         <v>28.98999977111816</v>
@@ -5448,7 +5460,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5475,11 +5487,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>40.69454956054688</v>
+        <v>40.6945686340332</v>
       </c>
       <c r="C195" t="n">
         <v>43.72999954223633</v>
@@ -5504,11 +5516,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>52.92750930786133</v>
+        <v>52.9275016784668</v>
       </c>
       <c r="C196" t="n">
         <v>56.7400016784668</v>
@@ -5533,11 +5545,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>51.38837432861328</v>
+        <v>51.38836288452148</v>
       </c>
       <c r="C197" t="n">
         <v>55.09000015258789</v>
@@ -5562,11 +5574,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>64.65289306640625</v>
+        <v>64.65288543701172</v>
       </c>
       <c r="C198" t="n">
         <v>69.30999755859375</v>
@@ -5591,11 +5603,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>55.02733993530273</v>
+        <v>55.02734756469727</v>
       </c>
       <c r="C199" t="n">
         <v>58.88000106811523</v>
@@ -5620,11 +5632,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>61.44783020019531</v>
+        <v>61.44782638549805</v>
       </c>
       <c r="C200" t="n">
         <v>65.75</v>
@@ -5649,11 +5661,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>66.35430908203125</v>
+        <v>66.35429382324219</v>
       </c>
       <c r="C201" t="n">
         <v>71</v>
@@ -5678,11 +5690,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>57.54497146606445</v>
+        <v>57.54497528076172</v>
       </c>
       <c r="C202" t="n">
         <v>61.45000076293945</v>
@@ -5707,11 +5719,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>67.98639678955078</v>
+        <v>67.98640441894531</v>
       </c>
       <c r="C203" t="n">
         <v>72.59999847412109</v>
@@ -5736,11 +5748,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>65.07403564453125</v>
+        <v>65.07405090332031</v>
       </c>
       <c r="C204" t="n">
         <v>69.48999786376953</v>
@@ -5765,11 +5777,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>59.10771179199219</v>
+        <v>59.10771942138672</v>
       </c>
       <c r="C205" t="n">
         <v>62.9900016784668</v>
@@ -5794,7 +5806,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5823,11 +5835,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>54.95075225830078</v>
+        <v>54.95074844360352</v>
       </c>
       <c r="C207" t="n">
         <v>58.56000137329102</v>
@@ -5852,7 +5864,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5881,7 +5893,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5910,11 +5922,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>54.26337814331055</v>
+        <v>54.26337432861328</v>
       </c>
       <c r="C210" t="n">
         <v>57.65999984741211</v>
@@ -5939,11 +5951,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>55.50262451171875</v>
+        <v>55.50261688232422</v>
       </c>
       <c r="C211" t="n">
         <v>58.79999923706055</v>
@@ -5968,11 +5980,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>59.58981323242188</v>
+        <v>59.58979797363281</v>
       </c>
       <c r="C212" t="n">
         <v>63.13000106811523</v>
@@ -5997,7 +6009,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6026,11 +6038,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>61.41024398803711</v>
+        <v>61.41024017333984</v>
       </c>
       <c r="C214" t="n">
         <v>64.87999725341797</v>
@@ -6055,11 +6067,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>58.50442886352539</v>
+        <v>58.50443267822266</v>
       </c>
       <c r="C215" t="n">
         <v>61.81000137329102</v>
@@ -6084,11 +6096,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>55.98668670654297</v>
+        <v>55.98667907714844</v>
       </c>
       <c r="C216" t="n">
         <v>59.15000152587891</v>
@@ -6113,7 +6125,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6142,11 +6154,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>54.66539764404297</v>
+        <v>54.6653938293457</v>
       </c>
       <c r="C218" t="n">
         <v>57.56999969482422</v>
@@ -6171,11 +6183,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>57.55202102661133</v>
+        <v>57.5520133972168</v>
       </c>
       <c r="C219" t="n">
         <v>60.61000061035156</v>
@@ -6200,11 +6212,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>61.9340705871582</v>
+        <v>61.93406295776367</v>
       </c>
       <c r="C220" t="n">
         <v>64.98999786376953</v>
@@ -6229,11 +6241,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>63.02999877929688</v>
+        <v>63.02999114990234</v>
       </c>
       <c r="C221" t="n">
         <v>66.13999938964844</v>
@@ -6258,11 +6270,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>59.5611572265625</v>
+        <v>59.56115341186523</v>
       </c>
       <c r="C222" t="n">
         <v>62.5</v>
@@ -6287,11 +6299,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>60.28922653198242</v>
+        <v>60.28923034667969</v>
       </c>
       <c r="C223" t="n">
         <v>63.02999877929688</v>
@@ -6316,11 +6328,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>58.17532348632812</v>
+        <v>58.17532730102539</v>
       </c>
       <c r="C224" t="n">
         <v>60.81999969482422</v>
@@ -6345,7 +6357,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6374,11 +6386,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>49.50758743286133</v>
+        <v>49.50759124755859</v>
       </c>
       <c r="C226" t="n">
         <v>51.54000091552734</v>
@@ -6403,7 +6415,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6432,7 +6444,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6461,11 +6473,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>47.67686462402344</v>
+        <v>47.6768684387207</v>
       </c>
       <c r="C229" t="n">
         <v>49.40999984741211</v>
@@ -6490,7 +6502,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6519,11 +6531,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>47.12686157226562</v>
+        <v>47.12685775756836</v>
       </c>
       <c r="C231" t="n">
         <v>48.84000015258789</v>
@@ -6548,7 +6560,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6577,7 +6589,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6606,7 +6618,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6635,11 +6647,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>40.9708366394043</v>
+        <v>40.97083282470703</v>
       </c>
       <c r="C235" t="n">
         <v>42.0099983215332</v>
@@ -6664,7 +6676,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6693,7 +6705,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6722,7 +6734,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6751,7 +6763,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6780,7 +6792,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6809,7 +6821,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6838,7 +6850,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6867,7 +6879,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6896,7 +6908,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6925,7 +6937,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6954,7 +6966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6983,7 +6995,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7012,7 +7024,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7041,7 +7053,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7070,32 +7082,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>57.36000061035156</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="C250" t="n">
-        <v>57.36000061035156</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="D250" t="n">
-        <v>138979500</v>
+        <v>148823500</v>
       </c>
       <c r="E250" t="n">
         <v>6.459999999999999</v>
       </c>
       <c r="F250" t="n">
-        <v>8.879257060425939</v>
+        <v>8.986067993353027</v>
       </c>
       <c r="G250" t="n">
         <v>999637371</v>
       </c>
       <c r="H250" t="n">
-        <v>57339200210.69023</v>
+        <v>58028948623.88721</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1390299162795105</v>
+        <v>0.1488774872943401</v>
       </c>
     </row>
   </sheetData>
@@ -7127,75 +7139,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7231,13 +7243,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7273,13 +7285,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7315,13 +7327,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7357,13 +7369,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7399,13 +7411,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7483,13 +7495,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7525,13 +7537,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7558,7 +7570,7 @@
       <c r="I10" t="n">
         <v>5.326821497120922</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K10" t="n">
@@ -7571,13 +7583,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7604,7 +7616,7 @@
       <c r="I11" t="n">
         <v>5.892077735124761</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K11" t="n">
@@ -7617,13 +7629,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7650,7 +7662,7 @@
       <c r="I12" t="n">
         <v>6.773494241842611</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K12" t="n">
@@ -7663,13 +7675,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7696,7 +7708,7 @@
       <c r="I13" t="n">
         <v>7.453717850287909</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K13" t="n">
@@ -7709,13 +7721,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7742,7 +7754,7 @@
       <c r="I14" t="n">
         <v>7.971071017274474</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K14" t="n">
@@ -7755,13 +7767,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7788,7 +7800,7 @@
       <c r="I15" t="n">
         <v>7.990232245681383</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K15" t="n">
@@ -7801,13 +7813,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7834,7 +7846,7 @@
       <c r="I16" t="n">
         <v>7.424976007677544</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="K16" t="n">
@@ -7847,13 +7859,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7880,7 +7892,7 @@
       <c r="I17" t="n">
         <v>6.965106525911709</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K17" t="n">
@@ -7893,13 +7905,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7926,7 +7938,7 @@
       <c r="I18" t="n">
         <v>5.432208253358926</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="K18" t="n">
@@ -7939,13 +7951,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7972,7 +7984,7 @@
       <c r="I19" t="n">
         <v>5.202273512476008</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="K19" t="n">
@@ -7985,13 +7997,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8018,7 +8030,7 @@
       <c r="I20" t="n">
         <v>5.202273512476008</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="K20" t="n">
@@ -8031,13 +8043,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8064,7 +8076,7 @@
       <c r="I21" t="n">
         <v>5.460950095969291</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="K21" t="n">
@@ -8077,13 +8089,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8110,7 +8122,7 @@
       <c r="I22" t="n">
         <v>7.013009596928984</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="K22" t="n">
@@ -8123,13 +8135,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8156,7 +8168,7 @@
       <c r="I23" t="n">
         <v>7.080073896353168</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="K23" t="n">
@@ -8169,13 +8181,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8202,7 +8214,7 @@
       <c r="I24" t="n">
         <v>7.252524952015357</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K24" t="n">
@@ -8215,13 +8227,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8248,7 +8260,7 @@
       <c r="I25" t="n">
         <v>6.859719769673706</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="K25" t="n">
@@ -8261,13 +8273,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42058</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8294,7 +8306,7 @@
       <c r="I26" t="n">
         <v>0.7886570000000006</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42058</v>
       </c>
       <c r="K26" t="n">
@@ -8307,13 +8319,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8340,7 +8352,7 @@
       <c r="I27" t="n">
         <v>-1.167474485604606</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K27" t="n">
@@ -8353,13 +8365,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8386,7 +8398,7 @@
       <c r="I28" t="n">
         <v>-2.681537270633397</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K28" t="n">
@@ -8399,13 +8411,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8432,7 +8444,7 @@
       <c r="I29" t="n">
         <v>-7.580718472168906</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K29" t="n">
@@ -8445,13 +8457,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8478,7 +8490,7 @@
       <c r="I30" t="n">
         <v>-10.23</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K30" t="n">
@@ -8491,13 +8503,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8524,7 +8536,7 @@
       <c r="I31" t="n">
         <v>-9.850476</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K31" t="n">
@@ -8537,13 +8549,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8570,7 +8582,7 @@
       <c r="I32" t="n">
         <v>-10.260085</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K32" t="n">
@@ -8583,13 +8595,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8616,7 +8628,7 @@
       <c r="I33" t="n">
         <v>-7.165899</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="K33" t="n">
@@ -8629,13 +8641,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8662,7 +8674,7 @@
       <c r="I34" t="n">
         <v>-0.75</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K34" t="n">
@@ -8675,13 +8687,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8708,7 +8720,7 @@
       <c r="I35" t="n">
         <v>-0.7</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K35" t="n">
@@ -8721,13 +8733,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8754,7 +8766,7 @@
       <c r="I36" t="n">
         <v>0.14</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K36" t="n">
@@ -8767,13 +8779,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8800,7 +8812,7 @@
       <c r="I37" t="n">
         <v>0.7100000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K37" t="n">
@@ -8813,13 +8825,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8846,7 +8858,7 @@
       <c r="I38" t="n">
         <v>1.7</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="K38" t="n">
@@ -8859,13 +8871,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8892,7 +8904,7 @@
       <c r="I39" t="n">
         <v>2.47</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="K39" t="n">
@@ -8905,13 +8917,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8938,7 +8950,7 @@
       <c r="I40" t="n">
         <v>2.91</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="K40" t="n">
@@ -8951,13 +8963,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8984,7 +8996,7 @@
       <c r="I41" t="n">
         <v>5.1</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="K41" t="n">
@@ -8997,13 +9009,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9030,7 +9042,7 @@
       <c r="I42" t="n">
         <v>5.390000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K42" t="n">
@@ -9043,13 +9055,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9076,7 +9088,7 @@
       <c r="I43" t="n">
         <v>5.31</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="K43" t="n">
@@ -9089,13 +9101,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9122,7 +9134,7 @@
       <c r="I44" t="n">
         <v>5.05</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K44" t="n">
@@ -9135,13 +9147,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9168,7 +9180,7 @@
       <c r="I45" t="n">
         <v>1.53</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="K45" t="n">
@@ -9181,13 +9193,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9214,7 +9226,7 @@
       <c r="I46" t="n">
         <v>-1.22</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="K46" t="n">
@@ -9227,13 +9239,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9260,7 +9272,7 @@
       <c r="I47" t="n">
         <v>-4.550000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K47" t="n">
@@ -9273,13 +9285,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44053</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9306,7 +9318,7 @@
       <c r="I48" t="n">
         <v>-14.51</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44053</v>
       </c>
       <c r="K48" t="n">
@@ -9319,13 +9331,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44144</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9352,7 +9364,7 @@
       <c r="I49" t="n">
         <v>-17.5</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44144</v>
       </c>
       <c r="K49" t="n">
@@ -9365,13 +9377,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9398,7 +9410,7 @@
       <c r="I50" t="n">
         <v>-17.06</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="K50" t="n">
@@ -9411,13 +9423,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44326</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9444,7 +9456,7 @@
       <c r="I51" t="n">
         <v>-14.93</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44326</v>
       </c>
       <c r="K51" t="n">
@@ -9457,13 +9469,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9490,7 +9502,7 @@
       <c r="I52" t="n">
         <v>-5.909999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="K52" t="n">
@@ -9503,13 +9515,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9536,7 +9548,7 @@
       <c r="I53" t="n">
         <v>-1.189999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K53" t="n">
@@ -9549,13 +9561,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9582,7 +9594,7 @@
       <c r="I54" t="n">
         <v>1.58</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K54" t="n">
@@ -9595,13 +9607,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44691</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9628,7 +9640,7 @@
       <c r="I55" t="n">
         <v>6.59</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44691</v>
       </c>
       <c r="K55" t="n">
@@ -9641,13 +9653,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9674,7 +9686,7 @@
       <c r="I56" t="n">
         <v>10.16</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="K56" t="n">
@@ -9687,13 +9699,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44873</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9720,7 +9732,7 @@
       <c r="I57" t="n">
         <v>12.03</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44873</v>
       </c>
       <c r="K57" t="n">
@@ -9733,13 +9745,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9766,7 +9778,7 @@
       <c r="I58" t="n">
         <v>12.4</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="K58" t="n">
@@ -9779,13 +9791,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9812,7 +9824,7 @@
       <c r="I59" t="n">
         <v>8.75</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="K59" t="n">
@@ -9825,13 +9837,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9858,7 +9870,7 @@
       <c r="I60" t="n">
         <v>5.909999999999998</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K60" t="n">
@@ -9871,13 +9883,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9904,7 +9916,7 @@
       <c r="I61" t="n">
         <v>4.589999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="K61" t="n">
@@ -9917,13 +9929,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9950,7 +9962,7 @@
       <c r="I62" t="n">
         <v>3.899999999999999</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="K62" t="n">
@@ -9963,13 +9975,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9996,7 +10008,7 @@
       <c r="I63" t="n">
         <v>3.649999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="K63" t="n">
@@ -10009,13 +10021,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10042,7 +10054,7 @@
       <c r="I64" t="n">
         <v>4.049999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K64" t="n">
@@ -10055,13 +10067,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10088,7 +10100,7 @@
       <c r="I65" t="n">
         <v>3.829999999999999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="K65" t="n">
@@ -10101,13 +10113,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10134,7 +10146,7 @@
       <c r="I66" t="n">
         <v>2.44</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="K66" t="n">
@@ -10147,13 +10159,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10180,7 +10192,7 @@
       <c r="I67" t="n">
         <v>2.459999999999999</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K67" t="n">
@@ -10193,13 +10205,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10226,7 +10238,7 @@
       <c r="I68" t="n">
         <v>1.689999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K68" t="n">
@@ -10239,13 +10251,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10272,7 +10284,7 @@
       <c r="I69" t="n">
         <v>1.359999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="K69" t="n">
@@ -10285,13 +10297,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10318,7 +10330,7 @@
       <c r="I70" t="n">
         <v>1.609999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="K70" t="n">
@@ -10331,13 +10343,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10364,7 +10376,7 @@
       <c r="I71" t="n">
         <v>3.969999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K71" t="n">
@@ -10377,13 +10389,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10410,7 +10422,7 @@
       <c r="I72" t="n">
         <v>6.459999999999999</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K72" t="n">
@@ -10447,52 +10459,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="C2" t="n">
@@ -10521,10 +10533,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="C3" t="n">
@@ -10553,10 +10565,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C4" t="n">
@@ -10585,10 +10597,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="C5" t="n">
@@ -10617,10 +10629,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="C6" t="n">
@@ -10649,10 +10661,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="C7" t="n">
@@ -10681,10 +10693,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C8" t="n">
@@ -10713,10 +10725,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C9" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C10" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C11" t="n">
@@ -10809,10 +10821,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C12" t="n">
@@ -10841,10 +10853,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="C13" t="n">
@@ -10873,10 +10885,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C14" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="C15" t="n">
@@ -10937,10 +10949,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C16" t="n">
@@ -10969,10 +10981,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="C17" t="n">
@@ -11001,10 +11013,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C18" t="n">
@@ -11033,10 +11045,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="C19" t="n">
@@ -11065,10 +11077,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="C20" t="n">
@@ -11097,10 +11109,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C21" t="n">
@@ -11129,10 +11141,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="C22" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42058</v>
       </c>
       <c r="C23" t="n">
@@ -11193,10 +11205,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C24" t="n">
@@ -11225,10 +11237,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C25" t="n">
@@ -11257,10 +11269,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C26" t="n">
@@ -11289,10 +11301,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C27" t="n">
@@ -11321,10 +11333,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C28" t="n">
@@ -11353,10 +11365,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C29" t="n">
@@ -11385,10 +11397,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C30" t="n">
@@ -11417,10 +11429,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C31" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C32" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C33" t="n">
@@ -11513,10 +11525,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C34" t="n">
@@ -11545,10 +11557,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="C35" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="C36" t="n">
@@ -11609,10 +11621,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="C37" t="n">
@@ -11641,10 +11653,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="C38" t="n">
@@ -11673,10 +11685,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C39" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="C40" t="n">
@@ -11737,10 +11749,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43657</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C41" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="C42" t="n">
@@ -11801,10 +11813,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="C43" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43924</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C44" t="n">
@@ -11865,10 +11877,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44053</v>
       </c>
       <c r="C45" t="n">
@@ -11897,10 +11909,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44144</v>
       </c>
       <c r="C46" t="n">
@@ -11929,10 +11941,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C47" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44326</v>
       </c>
       <c r="C48" t="n">
@@ -11993,10 +12005,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="C49" t="n">
@@ -12025,10 +12037,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C50" t="n">
@@ -12057,10 +12069,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C51" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44691</v>
       </c>
       <c r="C52" t="n">
@@ -12121,10 +12133,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C53" t="n">
@@ -12153,10 +12165,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44873</v>
       </c>
       <c r="C54" t="n">
@@ -12185,10 +12197,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C55" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="C56" t="n">
@@ -12249,10 +12261,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C57" t="n">
@@ -12281,10 +12293,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="C58" t="n">
@@ -12313,10 +12325,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="C59" t="n">
@@ -12345,10 +12357,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="C60" t="n">
@@ -12377,10 +12389,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C61" t="n">
@@ -12409,10 +12421,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="C62" t="n">
@@ -12441,10 +12453,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C63" t="n">
@@ -12473,10 +12485,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C64" t="n">
@@ -12505,10 +12517,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C65" t="n">
@@ -12537,10 +12549,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="C66" t="n">
@@ -12569,10 +12581,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="C67" t="n">
@@ -12601,10 +12613,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C68" t="n">
@@ -12633,10 +12645,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C69" t="n">
@@ -12683,12 +12695,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/OXY.xlsx
+++ b/salidas/empresas/OXY.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>27.36649322509766</v>
+        <v>27.36648368835449</v>
       </c>
       <c r="C2" t="n">
         <v>46.80609130859375</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>26.05231094360352</v>
+        <v>26.05229949951172</v>
       </c>
       <c r="C4" t="n">
         <v>44.38219451904297</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>28.88951301574707</v>
+        <v>28.88951683044434</v>
       </c>
       <c r="C5" t="n">
         <v>49.21561431884766</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>27.86318588256836</v>
+        <v>27.8631649017334</v>
       </c>
       <c r="C6" t="n">
         <v>47.4671516418457</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>28.94225120544434</v>
+        <v>28.94224548339844</v>
       </c>
       <c r="C7" t="n">
         <v>49.12459945678711</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>30.40982437133789</v>
+        <v>30.40982246398926</v>
       </c>
       <c r="C8" t="n">
         <v>51.61555862426758</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>28.7813835144043</v>
+        <v>28.7813720703125</v>
       </c>
       <c r="C9" t="n">
         <v>48.8515510559082</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>27.27325057983398</v>
+        <v>27.27325630187988</v>
       </c>
       <c r="C10" t="n">
         <v>46.09233474731445</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>26.60999488830566</v>
+        <v>26.60998153686523</v>
       </c>
       <c r="C11" t="n">
         <v>44.97140121459961</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>28.53742027282715</v>
+        <v>28.53742599487305</v>
       </c>
       <c r="C12" t="n">
         <v>48.22881317138672</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>27.80233764648438</v>
+        <v>27.80233192443848</v>
       </c>
       <c r="C13" t="n">
         <v>46.78213882446289</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>26.39598846435547</v>
+        <v>26.3959846496582</v>
       </c>
       <c r="C14" t="n">
         <v>44.41572570800781</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>26.25934219360352</v>
+        <v>26.25935554504395</v>
       </c>
       <c r="C15" t="n">
         <v>44.18579483032227</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>28.21111297607422</v>
+        <v>28.21112251281738</v>
       </c>
       <c r="C16" t="n">
         <v>47.24200820922852</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>29.0063591003418</v>
+        <v>29.00637054443359</v>
       </c>
       <c r="C17" t="n">
         <v>48.57371520996094</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>31.44930839538574</v>
+        <v>31.44929695129395</v>
       </c>
       <c r="C18" t="n">
         <v>52.66463470458984</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>33.23958206176758</v>
+        <v>33.23957824707031</v>
       </c>
       <c r="C19" t="n">
         <v>55.45259475708008</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.57339859008789</v>
+        <v>32.57340240478516</v>
       </c>
       <c r="C20" t="n">
         <v>54.34124374389648</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>32.55617141723633</v>
+        <v>32.55619049072266</v>
       </c>
       <c r="C21" t="n">
         <v>54.31250381469727</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>36.95844650268555</v>
+        <v>36.95844268798828</v>
       </c>
       <c r="C22" t="n">
         <v>61.39257431030273</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>39.82489395141602</v>
+        <v>39.82492065429688</v>
       </c>
       <c r="C23" t="n">
         <v>66.15414428710938</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>44.56280136108398</v>
+        <v>44.56280899047852</v>
       </c>
       <c r="C25" t="n">
         <v>73.76114654541016</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>39.24351501464844</v>
+        <v>39.24352264404297</v>
       </c>
       <c r="C26" t="n">
         <v>64.95656585693359</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>42.48712158203125</v>
+        <v>42.48712921142578</v>
       </c>
       <c r="C28" t="n">
         <v>70.10135650634766</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>48.31696319580078</v>
+        <v>48.31698608398438</v>
       </c>
       <c r="C29" t="n">
         <v>79.72029113769531</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>53.38035202026367</v>
+        <v>53.38037490844727</v>
       </c>
       <c r="C30" t="n">
         <v>88.0745849609375</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>52.36123657226562</v>
+        <v>52.36123275756836</v>
       </c>
       <c r="C31" t="n">
         <v>86.09140014648438</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>45.9340705871582</v>
+        <v>45.93407821655273</v>
       </c>
       <c r="C32" t="n">
         <v>75.52397918701172</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>46.2429084777832</v>
+        <v>46.24288940429688</v>
       </c>
       <c r="C33" t="n">
         <v>76.03175354003906</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>31.6856517791748</v>
+        <v>31.6856575012207</v>
       </c>
       <c r="C36" t="n">
         <v>51.86944580078125</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>35.35430908203125</v>
+        <v>35.35431289672852</v>
       </c>
       <c r="C37" t="n">
         <v>57.47410583496094</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>32.1483268737793</v>
+        <v>32.14831161499023</v>
       </c>
       <c r="C38" t="n">
         <v>52.26224899291992</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>30.56890106201172</v>
+        <v>30.56890869140625</v>
       </c>
       <c r="C39" t="n">
         <v>49.69464492797852</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>33.0076789855957</v>
+        <v>33.00767135620117</v>
       </c>
       <c r="C40" t="n">
         <v>53.31611633300781</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>33.38727569580078</v>
+        <v>33.38728332519531</v>
       </c>
       <c r="C41" t="n">
         <v>53.92927551269531</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>39.80493927001953</v>
+        <v>39.804931640625</v>
       </c>
       <c r="C42" t="n">
         <v>64.29550170898438</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>39.22266006469727</v>
+        <v>39.22265625</v>
       </c>
       <c r="C43" t="n">
         <v>63.05002212524414</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>42.5185432434082</v>
+        <v>42.51853942871094</v>
       </c>
       <c r="C44" t="n">
         <v>68.34809875488281</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>43.56748199462891</v>
+        <v>43.5674934387207</v>
       </c>
       <c r="C45" t="n">
         <v>70.03428649902344</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>45.43049621582031</v>
+        <v>45.43048858642578</v>
       </c>
       <c r="C47" t="n">
         <v>72.69770050048828</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>48.37018966674805</v>
+        <v>48.37017822265625</v>
       </c>
       <c r="C48" t="n">
         <v>77.40177917480469</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>48.91176986694336</v>
+        <v>48.9117546081543</v>
       </c>
       <c r="C49" t="n">
         <v>77.93829345703125</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>47.10200881958008</v>
+        <v>47.10201644897461</v>
       </c>
       <c r="C50" t="n">
         <v>75.05453491210938</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>48.00990295410156</v>
+        <v>48.00988006591797</v>
       </c>
       <c r="C51" t="n">
         <v>76.50120544433594</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>51.03530120849609</v>
+        <v>51.03529739379883</v>
       </c>
       <c r="C52" t="n">
         <v>80.99451446533203</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>53.52248382568359</v>
+        <v>53.5224609375</v>
       </c>
       <c r="C53" t="n">
         <v>84.94172668457031</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>49.80982208251953</v>
+        <v>49.80981826782227</v>
       </c>
       <c r="C54" t="n">
         <v>79.04964447021484</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>46.79994201660156</v>
+        <v>46.79995727539062</v>
       </c>
       <c r="C55" t="n">
         <v>73.91443634033203</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>47.27310943603516</v>
+        <v>47.27310180664062</v>
       </c>
       <c r="C56" t="n">
         <v>74.66172790527344</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>44.33103179931641</v>
+        <v>44.33103561401367</v>
       </c>
       <c r="C57" t="n">
         <v>70.01512908935547</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>47.73481750488281</v>
+        <v>47.73482894897461</v>
       </c>
       <c r="C58" t="n">
         <v>75.01621246337891</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>53.75197219848633</v>
+        <v>53.751953125</v>
       </c>
       <c r="C60" t="n">
         <v>84.47227478027344</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>60.05180358886719</v>
+        <v>60.05179977416992</v>
       </c>
       <c r="C61" t="n">
         <v>93.98582458496094</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>59.18254089355469</v>
+        <v>59.18256759643555</v>
       </c>
       <c r="C62" t="n">
         <v>92.62538146972656</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>62.42082595825195</v>
+        <v>62.42081069946289</v>
       </c>
       <c r="C63" t="n">
         <v>97.69351959228516</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>64.24890899658203</v>
+        <v>64.2489013671875</v>
       </c>
       <c r="C64" t="n">
         <v>100.1078414916992</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>64.26357269287109</v>
+        <v>64.26355743408203</v>
       </c>
       <c r="C67" t="n">
         <v>99.67671203613281</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>60.64393997192383</v>
+        <v>60.64396286010742</v>
       </c>
       <c r="C68" t="n">
         <v>94.06246948242188</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>53.57768249511719</v>
+        <v>53.57767105102539</v>
       </c>
       <c r="C69" t="n">
         <v>83.10224914550781</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>44.41118240356445</v>
+        <v>44.41119003295898</v>
       </c>
       <c r="C70" t="n">
         <v>68.50138854980469</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>57.72830963134766</v>
+        <v>57.72831344604492</v>
       </c>
       <c r="C71" t="n">
         <v>89.04222869873047</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>61.43026733398438</v>
+        <v>61.43030166625977</v>
       </c>
       <c r="C72" t="n">
         <v>94.75227355957031</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>58.47724533081055</v>
+        <v>58.47724914550781</v>
       </c>
       <c r="C73" t="n">
         <v>89.77035522460938</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>65.13628387451172</v>
+        <v>65.13626098632812</v>
       </c>
       <c r="C75" t="n">
         <v>99.99286651611328</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>59.75148010253906</v>
+        <v>59.7514533996582</v>
       </c>
       <c r="C76" t="n">
         <v>91.23619079589844</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>57.23540115356445</v>
+        <v>57.23540878295898</v>
       </c>
       <c r="C77" t="n">
         <v>87.39436340332031</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>49.73746109008789</v>
+        <v>49.73746871948242</v>
       </c>
       <c r="C78" t="n">
         <v>75.94552612304688</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>54.17623519897461</v>
+        <v>54.17621994018555</v>
       </c>
       <c r="C79" t="n">
         <v>82.17292785644531</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>54.97208786010742</v>
+        <v>54.97209930419922</v>
       </c>
       <c r="C80" t="n">
         <v>83.38008880615234</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>53.69618988037109</v>
+        <v>53.69617080688477</v>
       </c>
       <c r="C81" t="n">
         <v>81.44480133056641</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>54.71688842773438</v>
+        <v>54.71691513061523</v>
       </c>
       <c r="C82" t="n">
         <v>82.45076751708984</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>50.20272827148438</v>
+        <v>50.20271301269531</v>
       </c>
       <c r="C83" t="n">
         <v>75.64852905273438</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>47.8184700012207</v>
+        <v>47.8184814453125</v>
       </c>
       <c r="C84" t="n">
         <v>72.05580139160156</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>49.06428146362305</v>
+        <v>49.06428909301758</v>
       </c>
       <c r="C85" t="n">
         <v>73.39708709716797</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>52.72760391235352</v>
+        <v>52.72761154174805</v>
       </c>
       <c r="C87" t="n">
         <v>78.877197265625</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>50.58408355712891</v>
+        <v>50.58411026000977</v>
       </c>
       <c r="C88" t="n">
         <v>75.08327484130859</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>57.61308670043945</v>
+        <v>57.61308288574219</v>
       </c>
       <c r="C89" t="n">
         <v>85.51656341552734</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>59.42680740356445</v>
+        <v>59.42678833007812</v>
       </c>
       <c r="C90" t="n">
         <v>88.20871734619141</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>57.99115371704102</v>
+        <v>57.99114227294922</v>
       </c>
       <c r="C91" t="n">
         <v>85.48782348632812</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>57.87418746948242</v>
+        <v>57.87418365478516</v>
       </c>
       <c r="C92" t="n">
         <v>85.31536865234375</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>57.32826614379883</v>
+        <v>57.32827377319336</v>
       </c>
       <c r="C93" t="n">
         <v>84.51059722900391</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>61.22893142700195</v>
+        <v>61.22893524169922</v>
       </c>
       <c r="C94" t="n">
         <v>89.6170654296875</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>62.89152908325195</v>
+        <v>62.89152145385742</v>
       </c>
       <c r="C95" t="n">
         <v>92.05054473876953</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>62.67941665649414</v>
+        <v>62.67942810058594</v>
       </c>
       <c r="C97" t="n">
         <v>91.11164093017578</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>63.6153564453125</v>
+        <v>63.61532974243164</v>
       </c>
       <c r="C99" t="n">
         <v>92.47209167480469</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>63.27504348754883</v>
+        <v>63.27505111694336</v>
       </c>
       <c r="C100" t="n">
         <v>91.29367065429688</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>63.58050155639648</v>
+        <v>63.58051300048828</v>
       </c>
       <c r="C101" t="n">
         <v>91.73438262939453</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>66.19676208496094</v>
+        <v>66.19675445556641</v>
       </c>
       <c r="C102" t="n">
         <v>95.50914001464844</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>68.63878631591797</v>
+        <v>68.6387939453125</v>
       </c>
       <c r="C103" t="n">
         <v>98.32584381103516</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>65.34832763671875</v>
+        <v>65.34828948974609</v>
       </c>
       <c r="C104" t="n">
         <v>93.6121826171875</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>64.76528167724609</v>
+        <v>64.7652587890625</v>
       </c>
       <c r="C106" t="n">
         <v>92.11760711669922</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>59.90196990966797</v>
+        <v>59.90199279785156</v>
       </c>
       <c r="C107" t="n">
         <v>85.20040130615234</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>53.73193740844727</v>
+        <v>53.73191833496094</v>
       </c>
       <c r="C108" t="n">
         <v>76.424560546875</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>57.08262252807617</v>
+        <v>57.08264923095703</v>
       </c>
       <c r="C109" t="n">
         <v>80.47296142578125</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>56.65068817138672</v>
+        <v>56.65068435668945</v>
       </c>
       <c r="C110" t="n">
         <v>79.86399841308594</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>55.14944076538086</v>
+        <v>55.14944839477539</v>
       </c>
       <c r="C111" t="n">
         <v>77.74760437011719</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>52.17856597900391</v>
+        <v>52.17858505249023</v>
       </c>
       <c r="C112" t="n">
         <v>72.87590026855469</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>57.25347518920898</v>
+        <v>57.25347137451172</v>
       </c>
       <c r="C113" t="n">
         <v>79.96382904052734</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>55.88826370239258</v>
+        <v>55.88824844360352</v>
       </c>
       <c r="C114" t="n">
         <v>78.05707550048828</v>
@@ -3271,7 +3271,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>56.12020874023438</v>
+        <v>56.12023544311523</v>
       </c>
       <c r="C115" t="n">
         <v>77.63779449462891</v>
@@ -3298,7 +3298,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>50.6575927734375</v>
+        <v>50.65758514404297</v>
       </c>
       <c r="C116" t="n">
         <v>70.08065795898438</v>
@@ -3325,7 +3325,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>52.68532943725586</v>
+        <v>52.68533325195312</v>
       </c>
       <c r="C117" t="n">
         <v>72.88587951660156</v>
@@ -3379,7 +3379,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>54.37493133544922</v>
+        <v>54.37491226196289</v>
       </c>
       <c r="C119" t="n">
         <v>74.41328430175781</v>
@@ -3406,7 +3406,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>55.140869140625</v>
+        <v>55.14086532592773</v>
       </c>
       <c r="C120" t="n">
         <v>75.46149444580078</v>
@@ -3433,7 +3433,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>49.85910797119141</v>
+        <v>49.8591194152832</v>
       </c>
       <c r="C121" t="n">
         <v>67.49506378173828</v>
@@ -3460,7 +3460,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>50.75880813598633</v>
+        <v>50.75881195068359</v>
       </c>
       <c r="C122" t="n">
         <v>68.71298980712891</v>
@@ -3514,7 +3514,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>51.094482421875</v>
+        <v>51.09447860717773</v>
       </c>
       <c r="C124" t="n">
         <v>68.43000030517578</v>
@@ -3568,7 +3568,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>56.3286247253418</v>
+        <v>56.32860946655273</v>
       </c>
       <c r="C126" t="n">
         <v>75.44000244140625</v>
@@ -3595,7 +3595,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>56.97411346435547</v>
+        <v>56.97410583496094</v>
       </c>
       <c r="C127" t="n">
         <v>75.55999755859375</v>
@@ -3622,7 +3622,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>56.34826278686523</v>
+        <v>56.3482666015625</v>
       </c>
       <c r="C128" t="n">
         <v>74.73000335693359</v>
@@ -3649,7 +3649,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>57.94679641723633</v>
+        <v>57.94680023193359</v>
       </c>
       <c r="C129" t="n">
         <v>76.84999847412109</v>
@@ -3676,7 +3676,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>55.52447128295898</v>
+        <v>55.52448654174805</v>
       </c>
       <c r="C130" t="n">
         <v>72.91999816894531</v>
@@ -3703,7 +3703,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>55.51689147949219</v>
+        <v>55.51686477661133</v>
       </c>
       <c r="C131" t="n">
         <v>72.91000366210938</v>
@@ -3730,7 +3730,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>54.33662796020508</v>
+        <v>54.33664321899414</v>
       </c>
       <c r="C132" t="n">
         <v>71.36000061035156</v>
@@ -3784,7 +3784,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>52.16611099243164</v>
+        <v>52.16612243652344</v>
       </c>
       <c r="C134" t="n">
         <v>67.76999664306641</v>
@@ -3811,7 +3811,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>50.45727157592773</v>
+        <v>50.4572639465332</v>
       </c>
       <c r="C135" t="n">
         <v>65.55000305175781</v>
@@ -3838,7 +3838,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>49.35123443603516</v>
+        <v>49.35121536254883</v>
       </c>
       <c r="C136" t="n">
         <v>63.36000061035156</v>
@@ -3892,7 +3892,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>45.90067291259766</v>
+        <v>45.90068817138672</v>
       </c>
       <c r="C138" t="n">
         <v>58.93000030517578</v>
@@ -3946,7 +3946,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>48.83946228027344</v>
+        <v>48.8394660949707</v>
       </c>
       <c r="C140" t="n">
         <v>61.93000030517578</v>
@@ -3973,7 +3973,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>47.08082962036133</v>
+        <v>47.08084487915039</v>
       </c>
       <c r="C141" t="n">
         <v>59.70000076293945</v>
@@ -4002,7 +4002,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>51.27578735351562</v>
+        <v>51.27579116821289</v>
       </c>
       <c r="C142" t="n">
         <v>64.20999908447266</v>
@@ -4031,7 +4031,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>51.56327438354492</v>
+        <v>51.56325912475586</v>
       </c>
       <c r="C143" t="n">
         <v>64.56999969482422</v>
@@ -4089,7 +4089,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>59.4820671081543</v>
+        <v>59.48208999633789</v>
       </c>
       <c r="C145" t="n">
         <v>73.66000366210938</v>
@@ -4118,7 +4118,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>60.53995513916016</v>
+        <v>60.5399284362793</v>
       </c>
       <c r="C146" t="n">
         <v>74.97000122070312</v>
@@ -4176,7 +4176,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>53.08364868164062</v>
+        <v>53.08363723754883</v>
       </c>
       <c r="C148" t="n">
         <v>64.95999908447266</v>
@@ -4205,7 +4205,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>63.13488388061523</v>
+        <v>63.1348876953125</v>
       </c>
       <c r="C149" t="n">
         <v>77.26000213623047</v>
@@ -4234,7 +4234,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>68.80606842041016</v>
+        <v>68.80607604980469</v>
       </c>
       <c r="C150" t="n">
         <v>84.19999694824219</v>
@@ -4263,7 +4263,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>68.99545288085938</v>
+        <v>68.99547576904297</v>
       </c>
       <c r="C151" t="n">
         <v>83.68000030517578</v>
@@ -4292,7 +4292,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>69.20160675048828</v>
+        <v>69.20159149169922</v>
       </c>
       <c r="C152" t="n">
         <v>83.93000030517578</v>
@@ -4321,7 +4321,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>65.85404968261719</v>
+        <v>65.85405731201172</v>
       </c>
       <c r="C153" t="n">
         <v>79.87000274658203</v>
@@ -4350,7 +4350,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>68.43862152099609</v>
+        <v>68.43865203857422</v>
       </c>
       <c r="C154" t="n">
         <v>82.16999816894531</v>
@@ -4379,7 +4379,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>55.86198425292969</v>
+        <v>55.86197662353516</v>
       </c>
       <c r="C155" t="n">
         <v>67.06999969482422</v>
@@ -4466,7 +4466,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>56.27048110961914</v>
+        <v>56.27047729492188</v>
       </c>
       <c r="C158" t="n">
         <v>66.77999877929688</v>
@@ -4495,7 +4495,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>55.7396354675293</v>
+        <v>55.73961639404297</v>
       </c>
       <c r="C159" t="n">
         <v>66.15000152587891</v>
@@ -4524,7 +4524,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>56.45154190063477</v>
+        <v>56.4515380859375</v>
       </c>
       <c r="C160" t="n">
         <v>66.19999694824219</v>
@@ -4582,7 +4582,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>42.44100189208984</v>
+        <v>42.44099426269531</v>
       </c>
       <c r="C162" t="n">
         <v>49.77000045776367</v>
@@ -4611,7 +4611,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>43.56887817382812</v>
+        <v>43.56887054443359</v>
       </c>
       <c r="C163" t="n">
         <v>50.27999877929688</v>
@@ -4640,7 +4640,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>44.50471496582031</v>
+        <v>44.50472259521484</v>
       </c>
       <c r="C164" t="n">
         <v>51.36000061035156</v>
@@ -4698,7 +4698,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>39.21586608886719</v>
+        <v>39.21585083007812</v>
       </c>
       <c r="C166" t="n">
         <v>44.47000122070312</v>
@@ -4727,7 +4727,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>35.71490859985352</v>
+        <v>35.71491622924805</v>
       </c>
       <c r="C167" t="n">
         <v>40.5</v>
@@ -4756,7 +4756,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>34.01293563842773</v>
+        <v>34.012939453125</v>
       </c>
       <c r="C168" t="n">
         <v>38.56999969482422</v>
@@ -4843,7 +4843,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>29.46853446960449</v>
+        <v>29.46853256225586</v>
       </c>
       <c r="C171" t="n">
         <v>32.7400016784668</v>
@@ -4870,7 +4870,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>10.73873996734619</v>
+        <v>10.73874092102051</v>
       </c>
       <c r="C172" t="n">
         <v>11.57999992370605</v>
@@ -4897,7 +4897,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>15.39404964447021</v>
+        <v>15.39404773712158</v>
       </c>
       <c r="C173" t="n">
         <v>16.60000038146973</v>
@@ -4924,7 +4924,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>12.00921440124512</v>
+        <v>12.0092134475708</v>
       </c>
       <c r="C174" t="n">
         <v>12.94999980926514</v>
@@ -4951,7 +4951,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>16.98030281066895</v>
+        <v>16.98030471801758</v>
       </c>
       <c r="C175" t="n">
         <v>18.29999923706055</v>
@@ -4978,7 +4978,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>14.60491466522217</v>
+        <v>14.6049165725708</v>
       </c>
       <c r="C176" t="n">
         <v>15.73999977111816</v>
@@ -5005,7 +5005,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>11.82125949859619</v>
+        <v>11.82126140594482</v>
       </c>
       <c r="C177" t="n">
         <v>12.73999977111816</v>
@@ -5059,7 +5059,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>8.479890823364258</v>
+        <v>8.479888916015625</v>
       </c>
       <c r="C179" t="n">
         <v>9.130000114440918</v>
@@ -5086,7 +5086,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>14.63779735565186</v>
+        <v>14.63779640197754</v>
       </c>
       <c r="C180" t="n">
         <v>15.76000022888184</v>
@@ -5113,7 +5113,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>16.08583068847656</v>
+        <v>16.08583641052246</v>
       </c>
       <c r="C181" t="n">
         <v>17.30999946594238</v>
@@ -5140,7 +5140,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>18.64135551452637</v>
+        <v>18.64135360717773</v>
       </c>
       <c r="C182" t="n">
         <v>20.05999946594238</v>
@@ -5167,7 +5167,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>24.72814178466797</v>
+        <v>24.72813987731934</v>
       </c>
       <c r="C183" t="n">
         <v>26.61000061035156</v>
@@ -5194,7 +5194,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>24.74574661254883</v>
+        <v>24.74574851989746</v>
       </c>
       <c r="C184" t="n">
         <v>26.6200008392334</v>
@@ -5221,7 +5221,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>23.57446098327637</v>
+        <v>23.57445335388184</v>
       </c>
       <c r="C185" t="n">
         <v>25.36000061035156</v>
@@ -5248,7 +5248,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>24.13221168518066</v>
+        <v>24.13221549987793</v>
       </c>
       <c r="C186" t="n">
         <v>25.95999908447266</v>
@@ -5275,7 +5275,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>29.07831382751465</v>
+        <v>29.07830429077148</v>
       </c>
       <c r="C187" t="n">
         <v>31.27000045776367</v>
@@ -5302,7 +5302,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>24.27066993713379</v>
+        <v>24.27066802978516</v>
       </c>
       <c r="C188" t="n">
         <v>26.10000038146973</v>
@@ -5329,7 +5329,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>23.88941192626953</v>
+        <v>23.889404296875</v>
       </c>
       <c r="C189" t="n">
         <v>25.69000053405762</v>
@@ -5356,7 +5356,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>27.5178108215332</v>
+        <v>27.51780700683594</v>
       </c>
       <c r="C190" t="n">
         <v>29.57999992370605</v>
@@ -5383,7 +5383,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>31.19243621826172</v>
+        <v>31.19242858886719</v>
       </c>
       <c r="C191" t="n">
         <v>33.52999877929688</v>
@@ -5410,7 +5410,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>27.58292579650879</v>
+        <v>27.58292770385742</v>
       </c>
       <c r="C192" t="n">
         <v>29.64999961853027</v>
@@ -5437,7 +5437,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>26.97770690917969</v>
+        <v>26.97771072387695</v>
       </c>
       <c r="C193" t="n">
         <v>28.98999977111816</v>
@@ -5491,7 +5491,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>40.6945686340332</v>
+        <v>40.69456481933594</v>
       </c>
       <c r="C195" t="n">
         <v>43.72999954223633</v>
@@ -5520,7 +5520,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>52.9275016784668</v>
+        <v>52.92750549316406</v>
       </c>
       <c r="C196" t="n">
         <v>56.7400016784668</v>
@@ -5549,7 +5549,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>51.38836288452148</v>
+        <v>51.38836669921875</v>
       </c>
       <c r="C197" t="n">
         <v>55.09000015258789</v>
@@ -5578,7 +5578,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>64.65288543701172</v>
+        <v>64.65290069580078</v>
       </c>
       <c r="C198" t="n">
         <v>69.30999755859375</v>
@@ -5607,7 +5607,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>55.02734756469727</v>
+        <v>55.02735137939453</v>
       </c>
       <c r="C199" t="n">
         <v>58.88000106811523</v>
@@ -5636,7 +5636,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>61.44782638549805</v>
+        <v>61.44783020019531</v>
       </c>
       <c r="C200" t="n">
         <v>65.75</v>
@@ -5694,7 +5694,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>57.54497528076172</v>
+        <v>57.54496383666992</v>
       </c>
       <c r="C202" t="n">
         <v>61.45000076293945</v>
@@ -5723,7 +5723,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>67.98640441894531</v>
+        <v>67.98641204833984</v>
       </c>
       <c r="C203" t="n">
         <v>72.59999847412109</v>
@@ -5752,7 +5752,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>65.07405090332031</v>
+        <v>65.07404327392578</v>
       </c>
       <c r="C204" t="n">
         <v>69.48999786376953</v>
@@ -5810,7 +5810,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>60.79677200317383</v>
+        <v>60.79677963256836</v>
       </c>
       <c r="C206" t="n">
         <v>64.79000091552734</v>
@@ -5897,7 +5897,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>57.9054069519043</v>
+        <v>57.90539932250977</v>
       </c>
       <c r="C209" t="n">
         <v>61.52999877929688</v>
@@ -5926,7 +5926,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>54.26337432861328</v>
+        <v>54.26338195800781</v>
       </c>
       <c r="C210" t="n">
         <v>57.65999984741211</v>
@@ -5984,7 +5984,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>59.58979797363281</v>
+        <v>59.58980560302734</v>
       </c>
       <c r="C212" t="n">
         <v>63.13000106811523</v>
@@ -6071,7 +6071,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>58.50443267822266</v>
+        <v>58.50442886352539</v>
       </c>
       <c r="C215" t="n">
         <v>61.81000137329102</v>
@@ -6100,7 +6100,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>55.98667907714844</v>
+        <v>55.9866828918457</v>
       </c>
       <c r="C216" t="n">
         <v>59.15000152587891</v>
@@ -6129,7 +6129,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>56.69742202758789</v>
+        <v>56.69741821289062</v>
       </c>
       <c r="C217" t="n">
         <v>59.70999908447266</v>
@@ -6187,7 +6187,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>57.5520133972168</v>
+        <v>57.55201721191406</v>
       </c>
       <c r="C219" t="n">
         <v>60.61000061035156</v>
@@ -6216,7 +6216,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>61.93406295776367</v>
+        <v>61.93407440185547</v>
       </c>
       <c r="C220" t="n">
         <v>64.98999786376953</v>
@@ -6274,7 +6274,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>59.56115341186523</v>
+        <v>59.56114959716797</v>
       </c>
       <c r="C222" t="n">
         <v>62.5</v>
@@ -6303,7 +6303,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>60.28923034667969</v>
+        <v>60.28922271728516</v>
       </c>
       <c r="C223" t="n">
         <v>63.02999877929688</v>
@@ -6332,7 +6332,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>58.17532730102539</v>
+        <v>58.17532348632812</v>
       </c>
       <c r="C224" t="n">
         <v>60.81999969482422</v>
@@ -6361,7 +6361,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>54.50230026245117</v>
+        <v>54.50231170654297</v>
       </c>
       <c r="C225" t="n">
         <v>56.97999954223633</v>
@@ -6390,7 +6390,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>49.50759124755859</v>
+        <v>49.50758743286133</v>
       </c>
       <c r="C226" t="n">
         <v>51.54000091552734</v>
@@ -6448,7 +6448,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>48.58544158935547</v>
+        <v>48.58544540405273</v>
       </c>
       <c r="C228" t="n">
         <v>50.58000183105469</v>
@@ -6535,7 +6535,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>47.12685775756836</v>
+        <v>47.12686157226562</v>
       </c>
       <c r="C231" t="n">
         <v>48.84000015258789</v>
@@ -6564,7 +6564,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>47.8718376159668</v>
+        <v>47.87183380126953</v>
       </c>
       <c r="C232" t="n">
         <v>49.36000061035156</v>
@@ -6593,7 +6593,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>38.22182083129883</v>
+        <v>38.22182464599609</v>
       </c>
       <c r="C233" t="n">
         <v>39.40999984741211</v>
@@ -6651,7 +6651,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>40.97083282470703</v>
+        <v>40.97084045410156</v>
       </c>
       <c r="C235" t="n">
         <v>42.0099983215332</v>
@@ -6680,7 +6680,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>42.85309600830078</v>
+        <v>42.85309982299805</v>
       </c>
       <c r="C236" t="n">
         <v>43.93999862670898</v>
@@ -6738,7 +6738,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>46.32753753662109</v>
+        <v>46.32752990722656</v>
       </c>
       <c r="C238" t="n">
         <v>47.25</v>
@@ -6767,7 +6767,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>40.39564895629883</v>
+        <v>40.39565277099609</v>
       </c>
       <c r="C239" t="n">
         <v>41.20000076293945</v>
@@ -6796,7 +6796,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>41.18003082275391</v>
+        <v>41.18003463745117</v>
       </c>
       <c r="C240" t="n">
         <v>42</v>
@@ -6854,7 +6854,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>44.76240539550781</v>
+        <v>44.76240158081055</v>
       </c>
       <c r="C242" t="n">
         <v>45.38999938964844</v>
@@ -6883,7 +6883,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>52.34607696533203</v>
+        <v>52.3460807800293</v>
       </c>
       <c r="C243" t="n">
         <v>53.08000183105469</v>
